--- a/data/trans_dic/P56$familiar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 81,47</t>
+          <t>16,47; 77,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 65,72</t>
+          <t>9,71; 65,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,5</t>
+          <t>0,0; 51,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,74; 63,98</t>
+          <t>21,25; 62,33</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,89</t>
+          <t>0,0; 59,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,65</t>
+          <t>0,0; 79,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 58,19</t>
+          <t>10,61; 57,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 64,57</t>
+          <t>16,04; 64,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,27</t>
+          <t>0,0; 47,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,79</t>
+          <t>0,0; 65,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,67; 52,2</t>
+          <t>18,44; 53,86</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 84,33</t>
+          <t>13,29; 85,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 85,07</t>
+          <t>13,32; 85,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,06; 74,87</t>
+          <t>29,99; 74,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 71,04</t>
+          <t>10,12; 70,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,04; 78,05</t>
+          <t>46,83; 77,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 62,72</t>
+          <t>8,1; 61,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,77; 64,99</t>
+          <t>17,63; 64,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 71,09</t>
+          <t>44,71; 71,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 34,28</t>
+          <t>5,62; 31,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 36,16</t>
+          <t>11,83; 37,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 40,84</t>
+          <t>7,05; 38,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,4; 64,61</t>
+          <t>42,28; 64,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,69</t>
+          <t>0,0; 55,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 49,24</t>
+          <t>6,47; 50,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,43</t>
+          <t>0,0; 46,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,15; 60,59</t>
+          <t>34,8; 61,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 29,39</t>
+          <t>6,72; 29,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,93; 36,58</t>
+          <t>12,64; 35,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 33,77</t>
+          <t>8,23; 33,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,16; 60,66</t>
+          <t>42,38; 59,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 63,93</t>
+          <t>8,19; 62,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,38; 59,95</t>
+          <t>17,22; 62,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 43,44</t>
+          <t>10,72; 44,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,03; 61,86</t>
+          <t>29,95; 62,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 55,61</t>
+          <t>7,15; 55,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,08; 47,87</t>
+          <t>24,05; 48,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 47,44</t>
+          <t>14,05; 48,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,86; 64,2</t>
+          <t>49,73; 64,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 46,63</t>
+          <t>11,61; 48,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,34; 47,24</t>
+          <t>25,13; 46,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,0; 38,74</t>
+          <t>16,26; 39,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,91; 61,75</t>
+          <t>47,69; 61,12</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 30,06</t>
+          <t>9,62; 29,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,82; 36,95</t>
+          <t>19,68; 37,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,38; 41,66</t>
+          <t>20,45; 40,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,25; 66,04</t>
+          <t>51,28; 65,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 30,06</t>
+          <t>9,62; 29,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,82; 36,95</t>
+          <t>19,68; 37,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,38; 41,66</t>
+          <t>20,45; 40,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,04; 66,79</t>
+          <t>53,8; 66,99</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,14; 32,15</t>
+          <t>10,28; 33,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,3; 37,43</t>
+          <t>16,04; 38,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,78; 26,46</t>
+          <t>9,76; 25,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,58; 59,03</t>
+          <t>43,89; 59,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 27,09</t>
+          <t>10,87; 28,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,44; 36,82</t>
+          <t>23,51; 36,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,36; 33,44</t>
+          <t>18,72; 33,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,97; 60,59</t>
+          <t>51,61; 60,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,33; 26,2</t>
+          <t>12,54; 26,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,5; 34,89</t>
+          <t>23,46; 34,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,46; 28,79</t>
+          <t>18,13; 29,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,73; 58,32</t>
+          <t>50,78; 58,79</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>958; 4662</t>
+          <t>942; 4442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>568; 3836</t>
+          <t>567; 3842</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1351</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4902</t>
+          <t>0; 3869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2129</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2398; 7395</t>
+          <t>2456; 7205</t>
         </is>
       </c>
     </row>
@@ -2135,32 +2135,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3848</t>
+          <t>0; 3897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 3862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>965; 5093</t>
+          <t>928; 5051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1442</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1475</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1450; 5234</t>
+          <t>1301; 5222</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1474</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4659</t>
+          <t>0; 4634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5968</t>
+          <t>0; 6133</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3148; 8801</t>
+          <t>3109; 9082</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>776; 5052</t>
+          <t>796; 5096</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>938; 6035</t>
+          <t>945; 6047</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1513</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4396; 10267</t>
+          <t>4112; 10157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1076; 7473</t>
+          <t>1065; 7458</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8303; 14077</t>
+          <t>8446; 13965</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>828; 6563</t>
+          <t>848; 6475</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3130; 11449</t>
+          <t>3106; 11400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1768</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14844; 22571</t>
+          <t>14195; 22685</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1752; 10098</t>
+          <t>1656; 9169</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4460; 15371</t>
+          <t>5029; 16123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2449; 10070</t>
+          <t>1738; 9562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21429; 32653</t>
+          <t>21370; 32757</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4390</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1101; 8970</t>
+          <t>1178; 9258</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9274</t>
+          <t>0; 10094</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9626; 17078</t>
+          <t>9810; 17333</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2490; 10817</t>
+          <t>2476; 10847</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8462; 22212</t>
+          <t>7676; 21403</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3916; 15711</t>
+          <t>3828; 15554</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33980; 47754</t>
+          <t>33364; 46762</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>807; 6550</t>
+          <t>839; 6433</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2246; 10877</t>
+          <t>3124; 11278</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2683; 11153</t>
+          <t>2752; 11423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5088; 11228</t>
+          <t>5436; 11417</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1157; 9599</t>
+          <t>1233; 9607</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15737; 31279</t>
+          <t>15715; 31692</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4903; 16968</t>
+          <t>5026; 17334</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41307; 53186</t>
+          <t>41196; 53015</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2816; 12825</t>
+          <t>3193; 13312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21152; 39438</t>
+          <t>20983; 38708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9828; 23803</t>
+          <t>9989; 24410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48382; 62364</t>
+          <t>48158; 61728</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1367; 2145</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5663; 18019</t>
+          <t>5765; 17511</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19501; 38288</t>
+          <t>20396; 39224</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19623; 40114</t>
+          <t>19691; 38561</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52900; 68170</t>
+          <t>52932; 68114</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5663; 18019</t>
+          <t>5765; 17511</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19501; 38288</t>
+          <t>20396; 39224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19623; 40114</t>
+          <t>19691; 38561</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55891; 70375</t>
+          <t>56689; 70582</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5379; 15524</t>
+          <t>4961; 16299</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12799; 29383</t>
+          <t>12593; 29885</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7052; 19077</t>
+          <t>7036; 18674</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43153; 58448</t>
+          <t>43464; 58678</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10506; 25341</t>
+          <t>10165; 26329</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47882; 75208</t>
+          <t>48021; 74484</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31316; 57040</t>
+          <t>31926; 57907</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>127951; 149179</t>
+          <t>127071; 149529</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18898; 37160</t>
+          <t>17788; 37377</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66466; 98669</t>
+          <t>66349; 97796</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42374; 69871</t>
+          <t>43997; 70873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>175159; 201334</t>
+          <t>175310; 202972</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiar-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,47; 77,63</t>
+          <t>17,65; 81,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 65,82</t>
+          <t>10,15; 67,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,71</t>
+          <t>0,0; 51,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 62,33</t>
+          <t>21,42; 62,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,63</t>
+          <t>0,0; 58,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,6</t>
+          <t>0,0; 81,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 57,71</t>
+          <t>11,23; 60,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,04; 64,41</t>
+          <t>15,33; 59,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,01</t>
+          <t>0,0; 47,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,56</t>
+          <t>0,0; 63,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,44; 53,86</t>
+          <t>17,8; 49,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 85,06</t>
+          <t>13,35; 84,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 85,24</t>
+          <t>13,36; 85,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,99; 74,07</t>
+          <t>33,47; 75,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,36</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 70,89</t>
+          <t>10,2; 70,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,83; 77,43</t>
+          <t>43,7; 76,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 61,89</t>
+          <t>9,22; 63,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,63; 64,72</t>
+          <t>17,86; 65,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,71; 71,45</t>
+          <t>46,05; 70,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 31,12</t>
+          <t>6,03; 34,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 37,93</t>
+          <t>12,48; 39,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 38,78</t>
+          <t>9,87; 39,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,28; 64,82</t>
+          <t>41,06; 63,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 50,83</t>
+          <t>6,52; 51,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,18</t>
+          <t>0,0; 49,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,8; 61,5</t>
+          <t>33,05; 60,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 29,46</t>
+          <t>7,17; 29,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 35,25</t>
+          <t>12,62; 35,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 33,44</t>
+          <t>8,0; 33,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,38; 59,4</t>
+          <t>43,05; 59,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 62,8</t>
+          <t>8,04; 64,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,22; 62,16</t>
+          <t>17,48; 59,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,72; 44,49</t>
+          <t>10,62; 41,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,95; 62,9</t>
+          <t>27,29; 61,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 55,66</t>
+          <t>6,76; 57,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,05; 48,5</t>
+          <t>24,06; 47,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 48,46</t>
+          <t>13,8; 44,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,73; 64,0</t>
+          <t>48,15; 64,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 48,4</t>
+          <t>10,89; 45,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,13; 46,36</t>
+          <t>25,72; 47,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,26; 39,73</t>
+          <t>14,95; 38,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,69; 61,12</t>
+          <t>47,71; 61,19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 29,22</t>
+          <t>8,5; 28,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 37,86</t>
+          <t>18,53; 35,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,45; 40,04</t>
+          <t>20,05; 40,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,28; 65,99</t>
+          <t>52,17; 66,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 29,22</t>
+          <t>8,5; 28,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 37,86</t>
+          <t>18,53; 35,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,45; 40,04</t>
+          <t>20,05; 40,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,8; 66,99</t>
+          <t>51,9; 66,12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 33,76</t>
+          <t>11,73; 33,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,04; 38,07</t>
+          <t>17,48; 38,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,9</t>
+          <t>9,72; 26,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,89; 59,26</t>
+          <t>42,42; 57,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,15</t>
+          <t>10,32; 27,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,51; 36,46</t>
+          <t>23,65; 36,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 33,95</t>
+          <t>18,27; 34,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,61; 60,73</t>
+          <t>50,81; 59,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 26,35</t>
+          <t>12,78; 26,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,46; 34,58</t>
+          <t>23,4; 34,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,13; 29,2</t>
+          <t>17,45; 29,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,78; 58,79</t>
+          <t>50,15; 57,86</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>5161</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>942; 4442</t>
+          <t>1043; 4829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>567; 3842</t>
+          <t>648; 4296</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 3828</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2456; 7205</t>
+          <t>2634; 7674</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6121</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3897</t>
+          <t>0; 3848</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 3962</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>928; 5051</t>
+          <t>1004; 5370</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1301; 5222</t>
+          <t>1484; 5732</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4634</t>
+          <t>0; 4690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6133</t>
+          <t>0; 5976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3109; 9082</t>
+          <t>3316; 9180</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>20454</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>796; 5096</t>
+          <t>800; 5069</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>945; 6047</t>
+          <t>948; 6073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4112; 10157</t>
+          <t>4770; 10730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3281</t>
+          <t>0; 4473</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1065; 7458</t>
+          <t>1073; 7445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8446; 13965</t>
+          <t>9065; 15860</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>848; 6475</t>
+          <t>965; 6674</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3106; 11400</t>
+          <t>3147; 11502</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14195; 22685</t>
+          <t>16115; 24797</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40843</t>
+          <t>43237</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1656; 9169</t>
+          <t>1775; 10267</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5029; 16123</t>
+          <t>5304; 16878</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1738; 9562</t>
+          <t>2433; 9719</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21370; 32757</t>
+          <t>22441; 34826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1178; 9258</t>
+          <t>1188; 9390</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 10094</t>
+          <t>0; 10724</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9810; 17333</t>
+          <t>9961; 18080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2476; 10847</t>
+          <t>2640; 10843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7676; 21403</t>
+          <t>7664; 21740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3828; 15554</t>
+          <t>3719; 15638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33364; 46762</t>
+          <t>36505; 50717</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>58950</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>839; 6433</t>
+          <t>824; 6566</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3124; 11278</t>
+          <t>3172; 10877</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2752; 11423</t>
+          <t>2726; 10613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5436; 11417</t>
+          <t>5121; 11479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1233; 9607</t>
+          <t>1167; 9878</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15715; 31692</t>
+          <t>15725; 30788</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5026; 17334</t>
+          <t>4937; 16031</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41196; 53015</t>
+          <t>43267; 57945</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3193; 13312</t>
+          <t>2994; 12536</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20983; 38708</t>
+          <t>21470; 39506</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9989; 24410</t>
+          <t>9187; 23860</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48158; 61728</t>
+          <t>51828; 66470</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61201</t>
+          <t>66381</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>68585</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5765; 17511</t>
+          <t>5097; 17263</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20396; 39224</t>
+          <t>19202; 37151</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19691; 38561</t>
+          <t>19306; 39041</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52932; 68114</t>
+          <t>58866; 74847</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5765; 17511</t>
+          <t>5097; 17263</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20396; 39224</t>
+          <t>19202; 37151</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19691; 38561</t>
+          <t>19306; 39041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>56689; 70582</t>
+          <t>59707; 76064</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50360</t>
+          <t>52898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>138347</t>
+          <t>149610</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>188706</t>
+          <t>202508</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4961; 16299</t>
+          <t>5663; 16148</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12593; 29885</t>
+          <t>13724; 29980</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7036; 18674</t>
+          <t>7008; 19030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43464; 58678</t>
+          <t>44425; 60642</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10165; 26329</t>
+          <t>9655; 25607</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48021; 74484</t>
+          <t>48310; 74795</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31926; 57907</t>
+          <t>31166; 58681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>127071; 149529</t>
+          <t>136996; 161441</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17788; 37377</t>
+          <t>18120; 37429</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66349; 97796</t>
+          <t>66160; 96571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43997; 70873</t>
+          <t>42344; 70591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>175310; 202972</t>
+          <t>187743; 216607</t>
         </is>
       </c>
     </row>
